--- a/marketing_forms/013_tracking_pixel_setup_survey--marketing_forms.xlsx
+++ b/marketing_forms/013_tracking_pixel_setup_survey--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_started',_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not Started', 'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'implemented',_'value':_'implemented'}</t>
+          <t>implemented</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Implemented', 'value': 'Implemented'}</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'enabled',_'value':_'enabled'}</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Enabled', 'value': 'Enabled'}</t>
+          <t>Enabled</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disabled',_'value':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disabled', 'value': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_required',_'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Required', 'value': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'enabled',_'value':_'enabled'}</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Enabled', 'value': 'Enabled'}</t>
+          <t>Enabled</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disabled',_'value':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disabled', 'value': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_required',_'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Required', 'value': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly', 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'utc',_'value':_'utc'}</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'UTC', 'value': 'UTC'}</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'gmt',_'value':_'gmt'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'GMT', 'value': 'GMT'}</t>
+          <t>GMT</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'local_time',_'value':_'local_time'}</t>
+          <t>local_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Local Time', 'value': 'Local Time'}</t>
+          <t>Local Time</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'utc',_'value':_'utc'}</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'UTC', 'value': 'UTC'}</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'gmt',_'value':_'gmt'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'GMT', 'value': 'GMT'}</t>
+          <t>GMT</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'local_time',_'value':_'local_time'}</t>
+          <t>local_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Local Time', 'value': 'Local Time'}</t>
+          <t>Local Time</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hours',_'value':_'hours'}</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hours', 'value': 'Hours'}</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'minutes',_'value':_'minutes'}</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Minutes', 'value': 'Minutes'}</t>
+          <t>Minutes</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'seconds',_'value':_'seconds'}</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Seconds', 'value': 'Seconds'}</t>
+          <t>Seconds</t>
         </is>
       </c>
     </row>
